--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -2946,7 +2946,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -2964,6 +2964,13 @@
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="20"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3505,17 +3505,17 @@
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="32.700624999999995" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30.270625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30.790625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.190625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:2" customFormat="1" ht="41.65" customHeight="1">
+    <x:row r="1" spans="1:2" customFormat="1" ht="41.503899765014644" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:2" customFormat="1" ht="28.05" customHeight="1">
+    <x:row r="2" spans="1:2" customFormat="1" ht="27.669266510009766" customHeight="1">
       <x:c r="A2" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -3566,25 +3566,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.130625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19.770881760040403" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20.576914475303873" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20.261586299027442" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="19.823491767124672" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19.265965043512054" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18.593249243200127" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17.810464139626163" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16.923567200086932" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="15.939308245815344" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14.865178081765206" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="13.70935148706247" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="12.480625000000002" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="11.18834997106968" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="9.84236139353867" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="8.4529030532120952" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="7.0305495670377383" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="5.5861259038858915" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="2.9306249999999996" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.150624999999998" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.315676440444804" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18.195145171689223" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17.902475307480557" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.495860622181581" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.978395699068074" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.3540187586588" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.627481686479374" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14.80431386834416" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.890780108391489" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12.893832950141361" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11.821059763441216" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10.680625000000003" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="9.48120805698084" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="8.2319372215478666" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="6.9423201990890719" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="5.6221717538374216" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="4.2815390125887012" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3663,25 +3663,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.130625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="53.700625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="75.182787353789848" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="74.59078007910469" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="73.609108708768659" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="72.245244354659377" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="70.509566848035433" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="68.415285742752957" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="65.978339782584669" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="63.217275597755666" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="60.153106553888612" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="56.809152827603185" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="53.210863925890891" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="49.385625000000012" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="45.362548427898965" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="41.172252251501526" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="36.846627154880053" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="32.418593756903711" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="27.921852065450746" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="2.9306249999999996" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.020625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="61.832985562903978" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="61.271495301031983" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="60.340427494313964" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="59.04686813095315" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="57.400661978777208" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="55.414337660610677" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="53.103012303890189" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="50.484276490196805" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="47.578060380308663" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="44.406482033643258" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="40.993679076470087" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="37.365625000000009" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="33.549931486433891" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="29.575638267388729" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="25.4729921140053" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="21.273216640756338" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="17.008274674887023" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3760,97 +3760,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" customFormat="1" ht="306" customHeight="1">
+    <x:row r="1" spans="1:1" customFormat="1" ht="304.36192512512207" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" customFormat="1" ht="15.299999999999999" customHeight="1">
+    <x:row r="2" spans="1:1" customFormat="1" ht="15.218096256256104" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" customFormat="1" ht="7.6499999999999986" customHeight="1">
+    <x:row r="3" spans="1:1" customFormat="1" ht="7.6090481281280509" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" customFormat="1" ht="16.15" customHeight="1">
+    <x:row r="4" spans="1:1" customFormat="1" ht="16.063546048270329" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" customFormat="1" ht="24.224999999999998" customHeight="1">
+    <x:row r="5" spans="1:1" customFormat="1" ht="24.095319072405495" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" customFormat="1" ht="32.3" customHeight="1">
+    <x:row r="6" spans="1:1" customFormat="1" ht="32.127092096540657" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" customFormat="1" ht="40.375" customHeight="1">
+    <x:row r="7" spans="1:1" customFormat="1" ht="40.158865120675834" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" customFormat="1" ht="48.449999999999996" customHeight="1">
+    <x:row r="8" spans="1:1" customFormat="1" ht="48.19063814481099" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" customFormat="1" ht="56.524999999999991" customHeight="1">
+    <x:row r="9" spans="1:1" customFormat="1" ht="56.222411168946159" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" customFormat="1" ht="64.6" customHeight="1">
+    <x:row r="10" spans="1:1" customFormat="1" ht="64.254184193081315" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" customFormat="1" ht="72.675" customHeight="1">
+    <x:row r="11" spans="1:1" customFormat="1" ht="72.285957217216492" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" customFormat="1" ht="80.75" customHeight="1">
+    <x:row r="12" spans="1:1" customFormat="1" ht="80.317730241351668" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" customFormat="1" ht="88.825" customHeight="1">
+    <x:row r="13" spans="1:1" customFormat="1" ht="88.349503265486845" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" customFormat="1" ht="96.899999999999991" customHeight="1">
+    <x:row r="14" spans="1:1" customFormat="1" ht="96.381276289621979" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" customFormat="1" ht="104.975" customHeight="1">
+    <x:row r="15" spans="1:1" customFormat="1" ht="104.41304931375716" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" customFormat="1" ht="113.04999999999998" customHeight="1">
+    <x:row r="16" spans="1:1" customFormat="1" ht="112.44482233789232" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" customFormat="1" ht="121.125" customHeight="1">
+    <x:row r="17" spans="1:1" customFormat="1" ht="120.4765953620275" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" customFormat="1" ht="129.2" customHeight="1">
+    <x:row r="18" spans="1:1" customFormat="1" ht="128.50836838616263" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" customFormat="1" ht="137.275" customHeight="1">
+    <x:row r="19" spans="1:1" customFormat="1" ht="136.54014141029782" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
@@ -3872,97 +3872,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" customFormat="1" ht="306" customHeight="1">
+    <x:row r="1" spans="1:1" customFormat="1" ht="304.36192512512207" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" customFormat="1" ht="81.6" customHeight="1">
+    <x:row r="2" spans="1:1" customFormat="1" ht="83.007799530029288" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" customFormat="1" ht="16.999999999999996" customHeight="1">
+    <x:row r="3" spans="1:1" customFormat="1" ht="17.2932915687561" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" customFormat="1" ht="33.999999999999993" customHeight="1">
+    <x:row r="4" spans="1:1" customFormat="1" ht="34.5865831375122" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" customFormat="1" ht="50.999999999999993" customHeight="1">
+    <x:row r="5" spans="1:1" customFormat="1" ht="51.8798747062683" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" customFormat="1" ht="67.999999999999986" customHeight="1">
+    <x:row r="6" spans="1:1" customFormat="1" ht="69.1731662750244" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" customFormat="1" ht="85" customHeight="1">
+    <x:row r="7" spans="1:1" customFormat="1" ht="86.466457843780518" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" customFormat="1" ht="101.99999999999999" customHeight="1">
+    <x:row r="8" spans="1:1" customFormat="1" ht="103.75974941253661" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" customFormat="1" ht="118.99999999999999" customHeight="1">
+    <x:row r="9" spans="1:1" customFormat="1" ht="121.0530409812927" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" customFormat="1" ht="135.99999999999997" customHeight="1">
+    <x:row r="10" spans="1:1" customFormat="1" ht="138.3463325500488" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" customFormat="1" ht="153" customHeight="1">
+    <x:row r="11" spans="1:1" customFormat="1" ht="155.6396241188049" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" customFormat="1" ht="170" customHeight="1">
+    <x:row r="12" spans="1:1" customFormat="1" ht="172.93291568756104" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" customFormat="1" ht="187" customHeight="1">
+    <x:row r="13" spans="1:1" customFormat="1" ht="190.22620725631714" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" customFormat="1" ht="203.99999999999997" customHeight="1">
+    <x:row r="14" spans="1:1" customFormat="1" ht="207.51949882507321" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" customFormat="1" ht="221" customHeight="1">
+    <x:row r="15" spans="1:1" customFormat="1" ht="224.81279039382932" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" customFormat="1" ht="237.99999999999997" customHeight="1">
+    <x:row r="16" spans="1:1" customFormat="1" ht="242.10608196258539" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" customFormat="1" ht="255" customHeight="1">
+    <x:row r="17" spans="1:1" customFormat="1" ht="259.39937353134155" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" customFormat="1" ht="271.99999999999994" customHeight="1">
+    <x:row r="18" spans="1:1" customFormat="1" ht="276.6926651000976" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" customFormat="1" ht="289" customHeight="1">
+    <x:row r="19" spans="1:1" customFormat="1" ht="293.98595666885376" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>60</x:v>
       </x:c>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3569,14 +3569,14 @@
     <x:col min="1" max="1" width="2.9306249999999996" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="16.150624999999998" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="17.315676440444804" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.195145171689223" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18.195145171689227" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="17.902475307480557" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="17.495860622181581" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="16.978395699068074" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="16.3540187586588" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="15.627481686479374" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14.80431386834416" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13.890780108391489" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14.804313868344162" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.890780108391487" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="12.893832950141361" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="11.821059763441216" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="10.680625000000003" style="0" customWidth="1"/>
@@ -3665,18 +3665,18 @@
   <x:cols>
     <x:col min="1" max="1" width="2.9306249999999996" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="51.020625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="61.832985562903978" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="61.832985562903971" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="61.271495301031983" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="60.340427494313964" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="59.04686813095315" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="57.400661978777208" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="55.414337660610677" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="60.340427494313957" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="59.046868130953143" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="57.400661978777215" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="55.41433766061067" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="53.103012303890189" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="50.484276490196805" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="50.484276490196812" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="47.578060380308663" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="44.406482033643258" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="40.993679076470087" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="37.365625000000009" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="40.99367907647008" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="37.365625" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="33.549931486433891" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="29.575638267388729" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="25.4729921140053" style="0" customWidth="1"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3004,206 +3004,206 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="39">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="21">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="255" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="5" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="10" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="15" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="20" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="25" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="30" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="35" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="40" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="45" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="50" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="55" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="60" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="65" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="80" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="85" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3509,17 +3509,15 @@
     <x:col min="2" max="2" width="28.190625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:2" customFormat="1" ht="41.503899765014644" customHeight="1">
+    <x:row r="1" spans="1:2" customFormat="1" ht="41.5039" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:2" customFormat="1" ht="27.669266510009766" customHeight="1">
+    </x:row>
+    <x:row r="2" spans="1:2" customFormat="1" ht="27.669267" customHeight="1">
       <x:c r="A2" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s"/>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="B4" s="0" t="s">
@@ -3566,25 +3564,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="2.9306249999999996" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.150624999999998" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17.315676440444804" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.195145171689227" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17.902475307480557" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17.495860622181581" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.978395699068074" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.3540187586588" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.627481686479374" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14.804313868344162" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13.890780108391487" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="12.893832950141361" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="11.821059763441216" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="10.680625000000003" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="9.48120805698084" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="8.2319372215478666" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="6.9423201990890719" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="5.6221717538374216" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="4.2815390125887012" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="2.930625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.150625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.315676" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18.195145" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17.902475" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.495861" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.978396" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.354019" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.627482" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14.804314" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.89078" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12.893833" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11.82106" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10.680625" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="9.481208" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="8.231937" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="6.94232" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="5.622172" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="4.281539" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3663,25 +3661,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="2.9306249999999996" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="2.930625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="51.020625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="61.832985562903971" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="61.271495301031983" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="60.340427494313957" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="59.046868130953143" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="57.400661978777215" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="55.41433766061067" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="53.103012303890189" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="50.484276490196812" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="47.578060380308663" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="44.406482033643258" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="40.99367907647008" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="61.832986" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="61.271495" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="60.340427" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="59.046868" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="57.400662" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="55.414338" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="53.103012" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="50.484276" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="47.57806" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="44.406482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="40.993679" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="37.365625" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="33.549931486433891" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="29.575638267388729" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="25.4729921140053" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="21.273216640756338" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="17.008274674887023" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="33.549931" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="29.575638" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="25.472992" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="21.273217" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="17.008275" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3760,97 +3758,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" customFormat="1" ht="304.36192512512207" customHeight="1">
+    <x:row r="1" spans="1:1" customFormat="1" ht="304.361925" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" customFormat="1" ht="15.218096256256104" customHeight="1">
+    <x:row r="2" spans="1:1" customFormat="1" ht="15.218096" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" customFormat="1" ht="7.6090481281280509" customHeight="1">
+    <x:row r="3" spans="1:1" customFormat="1" ht="7.609048" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" customFormat="1" ht="16.063546048270329" customHeight="1">
+    <x:row r="4" spans="1:1" customFormat="1" ht="16.063546" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" customFormat="1" ht="24.095319072405495" customHeight="1">
+    <x:row r="5" spans="1:1" customFormat="1" ht="24.095319" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" customFormat="1" ht="32.127092096540657" customHeight="1">
+    <x:row r="6" spans="1:1" customFormat="1" ht="32.127092" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" customFormat="1" ht="40.158865120675834" customHeight="1">
+    <x:row r="7" spans="1:1" customFormat="1" ht="40.158865" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" customFormat="1" ht="48.19063814481099" customHeight="1">
+    <x:row r="8" spans="1:1" customFormat="1" ht="48.190638" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" customFormat="1" ht="56.222411168946159" customHeight="1">
+    <x:row r="9" spans="1:1" customFormat="1" ht="56.222411" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" customFormat="1" ht="64.254184193081315" customHeight="1">
+    <x:row r="10" spans="1:1" customFormat="1" ht="64.254184" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" customFormat="1" ht="72.285957217216492" customHeight="1">
+    <x:row r="11" spans="1:1" customFormat="1" ht="72.285957" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" customFormat="1" ht="80.317730241351668" customHeight="1">
+    <x:row r="12" spans="1:1" customFormat="1" ht="80.31773" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" customFormat="1" ht="88.349503265486845" customHeight="1">
+    <x:row r="13" spans="1:1" customFormat="1" ht="88.349503" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" customFormat="1" ht="96.381276289621979" customHeight="1">
+    <x:row r="14" spans="1:1" customFormat="1" ht="96.381276" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" customFormat="1" ht="104.41304931375716" customHeight="1">
+    <x:row r="15" spans="1:1" customFormat="1" ht="104.413049" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" customFormat="1" ht="112.44482233789232" customHeight="1">
+    <x:row r="16" spans="1:1" customFormat="1" ht="112.444822" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" customFormat="1" ht="120.4765953620275" customHeight="1">
+    <x:row r="17" spans="1:1" customFormat="1" ht="120.476595" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" customFormat="1" ht="128.50836838616263" customHeight="1">
+    <x:row r="18" spans="1:1" customFormat="1" ht="128.508368" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" customFormat="1" ht="136.54014141029782" customHeight="1">
+    <x:row r="19" spans="1:1" customFormat="1" ht="136.540141" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
@@ -3872,97 +3870,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" customFormat="1" ht="304.36192512512207" customHeight="1">
+    <x:row r="1" spans="1:1" customFormat="1" ht="304.361925" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" customFormat="1" ht="83.007799530029288" customHeight="1">
+    <x:row r="2" spans="1:1" customFormat="1" ht="83.0078" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" customFormat="1" ht="17.2932915687561" customHeight="1">
+    <x:row r="3" spans="1:1" customFormat="1" ht="17.293292" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" customFormat="1" ht="34.5865831375122" customHeight="1">
+    <x:row r="4" spans="1:1" customFormat="1" ht="34.586583" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" customFormat="1" ht="51.8798747062683" customHeight="1">
+    <x:row r="5" spans="1:1" customFormat="1" ht="51.879875" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" customFormat="1" ht="69.1731662750244" customHeight="1">
+    <x:row r="6" spans="1:1" customFormat="1" ht="69.173166" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" customFormat="1" ht="86.466457843780518" customHeight="1">
+    <x:row r="7" spans="1:1" customFormat="1" ht="86.466458" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" customFormat="1" ht="103.75974941253661" customHeight="1">
+    <x:row r="8" spans="1:1" customFormat="1" ht="103.759749" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" customFormat="1" ht="121.0530409812927" customHeight="1">
+    <x:row r="9" spans="1:1" customFormat="1" ht="121.053041" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" customFormat="1" ht="138.3463325500488" customHeight="1">
+    <x:row r="10" spans="1:1" customFormat="1" ht="138.346333" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" customFormat="1" ht="155.6396241188049" customHeight="1">
+    <x:row r="11" spans="1:1" customFormat="1" ht="155.639624" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" customFormat="1" ht="172.93291568756104" customHeight="1">
+    <x:row r="12" spans="1:1" customFormat="1" ht="172.932916" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" customFormat="1" ht="190.22620725631714" customHeight="1">
+    <x:row r="13" spans="1:1" customFormat="1" ht="190.226207" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" customFormat="1" ht="207.51949882507321" customHeight="1">
+    <x:row r="14" spans="1:1" customFormat="1" ht="207.519499" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" customFormat="1" ht="224.81279039382932" customHeight="1">
+    <x:row r="15" spans="1:1" customFormat="1" ht="224.81279" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" customFormat="1" ht="242.10608196258539" customHeight="1">
+    <x:row r="16" spans="1:1" customFormat="1" ht="242.106082" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" customFormat="1" ht="259.39937353134155" customHeight="1">
+    <x:row r="17" spans="1:1" customFormat="1" ht="259.399374" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" customFormat="1" ht="276.6926651000976" customHeight="1">
+    <x:row r="18" spans="1:1" customFormat="1" ht="276.692665" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" customFormat="1" ht="293.98595666885376" customHeight="1">
+    <x:row r="19" spans="1:1" customFormat="1" ht="293.985957" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>60</x:v>
       </x:c>
